--- a/www/download/IND.surplus_value.empe_hs.r.pc.rpO2.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-87.77</t>
+          <t>-0.877720067196736</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-0.882528832693517</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-84.62</t>
+          <t>-0.846226306122498</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-0.852617237299259</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>-0.906965611560031</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-92.59</t>
+          <t>-0.925943104048963</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-91.7</t>
+          <t>-0.916996697075144</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-92.9</t>
+          <t>-0.929046094179556</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-92.97</t>
+          <t>-0.929678426397921</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.61</t>
+          <t>-0.906126363038661</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-93.95</t>
+          <t>-0.939471381665022</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-94.33</t>
+          <t>-0.943259329994295</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-94.53</t>
+          <t>-0.945337393949613</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-93.84</t>
+          <t>-0.938373694189427</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-91.54</t>
+          <t>-0.915427989006947</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-88.66</t>
+          <t>-0.886608639442633</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-89.17</t>
+          <t>-0.8916860802038</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-83.84</t>
+          <t>-0.83837767049056</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-85.54</t>
+          <t>-0.855387875814294</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-88.8</t>
+          <t>-0.888044484173111</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-91.44</t>
+          <t>-0.91444993624304</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-0.9218284485282</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-92.09</t>
+          <t>-0.920877881084777</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-0.918595060770718</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-92.12</t>
+          <t>-0.921204383706192</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-0.933070951267251</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-94.05</t>
+          <t>-0.940517533322751</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-92.78</t>
+          <t>-0.927767249458775</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-92.2</t>
+          <t>-0.921950148389309</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-88.76</t>
+          <t>-0.887645960796118</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-86.61</t>
+          <t>-0.866109915067833</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-0.845592143669344</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-80.12</t>
+          <t>-0.801186512598691</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-0.811411456236959</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-85.01</t>
+          <t>-0.850149559972997</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-89.37</t>
+          <t>-0.893729807419998</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-0.897669213796675</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-90.78</t>
+          <t>-0.907769503463628</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-91.39</t>
+          <t>-0.913891334495633</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>-0.919832584184776</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-93.35</t>
+          <t>-0.933540735012234</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-93.01</t>
+          <t>-0.930093833575639</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-91.34</t>
+          <t>-0.913377930238943</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-91.03</t>
+          <t>-0.91030363396788</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-88.15</t>
+          <t>-0.881460657137076</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-0.299944840000792</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-0.16979990232684</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>0.206967795306876</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-0.0981888255536184</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-23.28</t>
+          <t>-0.232753835601607</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-34.7</t>
+          <t>-0.346998549026545</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-43.18</t>
+          <t>-0.431819147437657</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.8</t>
+          <t>-0.507956612242533</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-47.37</t>
+          <t>-0.473747946456234</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-62.58</t>
+          <t>-0.6258446106115</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-65.77</t>
+          <t>-0.657676878070561</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-70.2</t>
+          <t>-0.702018591928059</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-66.5</t>
+          <t>-0.664951648126149</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-0.613221551327951</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-54.79</t>
+          <t>-0.547892171166248</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>0.15816560308549</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>0.153446106891615</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>0.246316691298318</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>0.201629896070416</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.235304766246426</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-0.170842464561194</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-0.20170328709467</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-0.0902334967151297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-0.108526951091816</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-0.197138404569034</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-25.46</t>
+          <t>-0.254646365938885</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-27.72</t>
+          <t>-0.277221640057934</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-0.217632886612892</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-0.240066344156579</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.045951471768956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-67.31</t>
+          <t>-0.673056981780884</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-69.07</t>
+          <t>-0.690736683214971</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-66.35</t>
+          <t>-0.663526874724043</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-71.23</t>
+          <t>-0.712292095475717</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.35</t>
+          <t>-0.773451974067066</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-85.8</t>
+          <t>-0.85803041407432</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-87.07</t>
+          <t>-0.870673599168453</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-85.46</t>
+          <t>-0.854597301036465</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-86.37</t>
+          <t>-0.863665383076534</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-86.09</t>
+          <t>-0.860863968219519</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-89.06</t>
+          <t>-0.890625254353816</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-88.48</t>
+          <t>-0.884775304581441</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-85.63</t>
+          <t>-0.85632626094735</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-84.48</t>
+          <t>-0.844804965181411</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-78.85</t>
+          <t>-0.788547180159006</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-0.404532803679802</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-39.85</t>
+          <t>-0.398492107530536</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-37.09</t>
+          <t>-0.370942288655301</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-35.15</t>
+          <t>-0.351547388855709</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.03</t>
+          <t>-0.340305544696025</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-35.81</t>
+          <t>-0.358143142758783</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-31.55</t>
+          <t>-0.315505008662715</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-0.283504569738584</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-0.257650861325439</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-25.54</t>
+          <t>-0.255396391863381</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-24.6</t>
+          <t>-0.24596372120123</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-0.231313906902834</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-0.139160584814909</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-13.14</t>
+          <t>-0.131406019691161</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-0.0588254826748699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-67.43</t>
+          <t>-0.674281853710573</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-72.27</t>
+          <t>-0.722698021393093</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-0.546108342377953</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-62.08</t>
+          <t>-0.620809795753079</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-75.75</t>
+          <t>-0.757531648835932</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-0.811442839259326</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-83.4</t>
+          <t>-0.834012018571483</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-0.840744175622849</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-83.34</t>
+          <t>-0.833391999973018</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-82.27</t>
+          <t>-0.822721999998374</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-0.778363266425776</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-73.39</t>
+          <t>-0.733919418264504</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-70.15</t>
+          <t>-0.701534508042169</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-63.97</t>
+          <t>-0.63973251423198</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-31.43</t>
+          <t>-0.31428980229784</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-39.55</t>
+          <t>-0.395452630758321</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-65.32</t>
+          <t>-0.653155068886956</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-48.5</t>
+          <t>-0.484956192195142</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-57.46</t>
+          <t>-0.57455739454668</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-66.46</t>
+          <t>-0.66462049600223</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.79</t>
+          <t>-0.747887524910172</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-81.69</t>
+          <t>-0.816878590616617</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-83.03</t>
+          <t>-0.830259636673352</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-83.06</t>
+          <t>-0.830591182203083</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-84.6</t>
+          <t>-0.846020498586426</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-87.04</t>
+          <t>-0.870383112734825</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-87.17</t>
+          <t>-0.871662642758654</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-84.15</t>
+          <t>-0.841470663995157</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-81.88</t>
+          <t>-0.818750308651029</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-69.03</t>
+          <t>-0.69029600226977</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-91.48</t>
+          <t>-0.91476602374242</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-90.5</t>
+          <t>-0.904950020948492</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-0.888544379348347</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-89.79</t>
+          <t>-0.897926068889304</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-92.06</t>
+          <t>-0.920556447324292</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-94.45</t>
+          <t>-0.944528710300395</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-95.05</t>
+          <t>-0.950540848657386</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-95.16</t>
+          <t>-0.951633490481952</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-95.46</t>
+          <t>-0.954596449306572</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.12</t>
+          <t>-0.951181343018503</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-95.47</t>
+          <t>-0.954732777443599</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-95.87</t>
+          <t>-0.958690821826251</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-94.8</t>
+          <t>-0.948017342134751</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-94.23</t>
+          <t>-0.942339814177653</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-91.8</t>
+          <t>-0.917959990187203</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-93.1</t>
+          <t>-0.930998010764542</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-92.67</t>
+          <t>-0.92671806444882</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-89.36</t>
+          <t>-0.893574974630345</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-90.05</t>
+          <t>-0.900534444799858</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-91.18</t>
+          <t>-0.911756836450899</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-0.924462597552204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>-0.930842985767891</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-93.48</t>
+          <t>-0.934759941660878</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-0.940392834310595</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-94.2</t>
+          <t>-0.941953327323892</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-94.72</t>
+          <t>-0.947229178434632</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-94.58</t>
+          <t>-0.945799970749949</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-0.936673581225643</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>-0.941081818817808</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-0.900414975315651</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-78.88</t>
+          <t>-0.788824026751153</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-79.18</t>
+          <t>-0.791802809164187</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-75.29</t>
+          <t>-0.752872538095471</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-77.13</t>
+          <t>-0.771276321392356</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-83.51</t>
+          <t>-0.835082225693143</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-89.02</t>
+          <t>-0.890172964365698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-89.56</t>
+          <t>-0.895558015357179</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-89.25</t>
+          <t>-0.892546791090116</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-89.41</t>
+          <t>-0.894146738822439</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-90.46</t>
+          <t>-0.904566638061793</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-91.84</t>
+          <t>-0.918374031804041</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-0.922096737084032</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-90.5</t>
+          <t>-0.904979572350836</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-89.74</t>
+          <t>-0.897402552435406</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-84.58</t>
+          <t>-0.845777809057137</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>163.13</t>
+          <t>1.6313239824904</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>146.49</t>
+          <t>1.46490686680332</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>266.29</t>
+          <t>2.66290088834317</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>241.18</t>
+          <t>2.41181604941212</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-47.76</t>
+          <t>-0.4775998747433</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-82.55</t>
+          <t>-0.8254989859295</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-83.27</t>
+          <t>-0.832737153394495</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-87.21</t>
+          <t>-0.872128963580489</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-91.48</t>
+          <t>-0.914771578423606</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-0.863485872253359</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-77.93</t>
+          <t>-0.779260995326919</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-84.63</t>
+          <t>-0.846309216179502</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-86.16</t>
+          <t>-0.861647946093724</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-86.01</t>
+          <t>-0.860109322164983</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-80.13</t>
+          <t>-0.801323521337109</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-81.38</t>
+          <t>-0.813793453798844</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-81.83</t>
+          <t>-0.818346467676055</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-74.25</t>
+          <t>-0.74246164778307</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-77.54</t>
+          <t>-0.775448362361011</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-83.64</t>
+          <t>-0.836420341640192</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-86.42</t>
+          <t>-0.86415847455467</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-88.1</t>
+          <t>-0.88103265078496</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-88.39</t>
+          <t>-0.883904195005171</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-0.906921772259168</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-91.39</t>
+          <t>-0.913931215521491</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-91.91</t>
+          <t>-0.919124138301771</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-92.17</t>
+          <t>-0.921715322235098</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-90.58</t>
+          <t>-0.905762750047406</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-90.34</t>
+          <t>-0.903368466615565</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-85.36</t>
+          <t>-0.853576426793888</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-91.81</t>
+          <t>-0.918143988374405</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-91.17</t>
+          <t>-0.911729623974102</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-0.886288508172876</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-89.04</t>
+          <t>-0.890441350274951</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-91.8</t>
+          <t>-0.918012734295166</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-94.18</t>
+          <t>-0.941773716378952</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-94.55</t>
+          <t>-0.94550644083007</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-0.947290707397535</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-94.98</t>
+          <t>-0.949822334111288</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-95.48</t>
+          <t>-0.954768690704517</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-96.19</t>
+          <t>-0.961920767735883</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-0.96166900405571</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-95.33</t>
+          <t>-0.953346710809202</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-95.01</t>
+          <t>-0.950059135384219</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-0.926232067186214</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-90.85</t>
+          <t>-0.908487049311998</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-90.47</t>
+          <t>-0.904697410625378</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-86.75</t>
+          <t>-0.867502299988755</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-0.87727524395216</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-90.68</t>
+          <t>-0.906845489287371</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-93.04</t>
+          <t>-0.93037945173062</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-93.62</t>
+          <t>-0.936185432083561</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-0.93588038209363</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-94.23</t>
+          <t>-0.942348275756642</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-94.43</t>
+          <t>-0.944292466332698</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-95.13</t>
+          <t>-0.951302210827778</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-95.4</t>
+          <t>-0.953974043698845</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-94.83</t>
+          <t>-0.948324573353715</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-94.36</t>
+          <t>-0.943585165607654</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-92.4</t>
+          <t>-0.923990294618077</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-51.23</t>
+          <t>-0.512269780468871</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-55.44</t>
+          <t>-0.554392383924814</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-0.399934578563206</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-46.37</t>
+          <t>-0.463668016392494</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-60.96</t>
+          <t>-0.609558331133018</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-0.781880253946279</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-81.44</t>
+          <t>-0.814437141483582</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-83.21</t>
+          <t>-0.832102962620489</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-85.16</t>
+          <t>-0.851578979251589</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-83.31</t>
+          <t>-0.833140008616432</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-88.06</t>
+          <t>-0.880641111738262</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-89.99</t>
+          <t>-0.89994069675644</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-0.879467488150038</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-87.46</t>
+          <t>-0.874582777913801</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-81.85</t>
+          <t>-0.818540075262514</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-62.62</t>
+          <t>-0.626169569960555</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-58.58</t>
+          <t>-0.585796727069678</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-44.07</t>
+          <t>-0.440713433295264</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-56.12</t>
+          <t>-0.56122091154499</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-67.8</t>
+          <t>-0.677962046852095</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.04</t>
+          <t>-0.710358117236024</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-77.2</t>
+          <t>-0.771996325254704</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-76.53</t>
+          <t>-0.765282347210654</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-78.18</t>
+          <t>-0.781802710058582</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-80.56</t>
+          <t>-0.805627057302676</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-81.71</t>
+          <t>-0.817094209790366</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-80.28</t>
+          <t>-0.802806740022916</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-78.44</t>
+          <t>-0.784381199620965</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-70.22</t>
+          <t>-0.702222679389044</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-47.8</t>
+          <t>-0.477995585426361</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>0.35900918905289</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>0.490911865781397</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>0.5731837619042</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>84.82</t>
+          <t>0.848225467886721</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>0.402985254970521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-20.91</t>
+          <t>-0.209145376310912</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>-0.258029955588896</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-0.237154250436899</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-32.83</t>
+          <t>-0.328338670034244</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-0.256908798299204</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-43.72</t>
+          <t>-0.437231268261014</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-49.2</t>
+          <t>-0.492036618634315</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-0.533092328006349</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-55.54</t>
+          <t>-0.555403069460046</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-43.11</t>
+          <t>-0.431128551024308</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>0.806802886028062</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>96.61</t>
+          <t>0.966104251806449</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>0.928595925248973</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>0.947751056459077</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>75.16</t>
+          <t>0.751564433045385</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66.01</t>
+          <t>0.660146318081597</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>0.708107565474778</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.43</t>
+          <t>0.764280020643204</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>82.65</t>
+          <t>0.82654912251247</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>82.93</t>
+          <t>0.829338384460824</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>83.48</t>
+          <t>0.834771475758311</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>0.853557409704115</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>92.29</t>
+          <t>0.922938705932349</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>104.95</t>
+          <t>1.04953554513682</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>113.37</t>
+          <t>1.13373086108611</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-76.9</t>
+          <t>-0.768959355081463</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-74.61</t>
+          <t>-0.746112048287399</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-79.54</t>
+          <t>-0.795442872333533</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-80.73</t>
+          <t>-0.807309305690137</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-83.47</t>
+          <t>-0.834749854758227</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-0.869607555432485</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-0.868471359104227</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-87.3</t>
+          <t>-0.873017861155265</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-89.6</t>
+          <t>-0.896033820993383</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-91.1</t>
+          <t>-0.911032641302777</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-93.22</t>
+          <t>-0.932239864891234</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-94.01</t>
+          <t>-0.940114454564126</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-93.26</t>
+          <t>-0.932561011131008</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-91.9</t>
+          <t>-0.918976171815329</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-91.24</t>
+          <t>-0.912394990520109</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-79.88</t>
+          <t>-0.798847464093722</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-80.13</t>
+          <t>-0.801327858379663</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-76.71</t>
+          <t>-0.767054090203827</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-77.28</t>
+          <t>-0.772759921650932</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-82.85</t>
+          <t>-0.828459511545894</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-88.13</t>
+          <t>-0.881296071156017</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-88.27</t>
+          <t>-0.882662988538296</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-88.18</t>
+          <t>-0.881794296546915</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-0.87483811520456</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-88.64</t>
+          <t>-0.886428292008019</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-90.22</t>
+          <t>-0.902233088678805</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-91.02</t>
+          <t>-0.910214527521385</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-88.72</t>
+          <t>-0.887154029013917</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-88.42</t>
+          <t>-0.884228792716835</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-83.67</t>
+          <t>-0.83672012302886</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-77.86</t>
+          <t>-0.778636624172915</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-77.97</t>
+          <t>-0.779653176433775</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-72.24</t>
+          <t>-0.722377323239205</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-0.696185180444943</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.14</t>
+          <t>-0.791362079641766</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-84.1</t>
+          <t>-0.840981226873622</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-84.99</t>
+          <t>-0.849858772291706</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-85.38</t>
+          <t>-0.853754919886161</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-86.8</t>
+          <t>-0.868037096081819</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-87.45</t>
+          <t>-0.874451544780026</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-89.09</t>
+          <t>-0.890904118959334</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-88.99</t>
+          <t>-0.889863834001357</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-86.11</t>
+          <t>-0.86112130474852</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-87.09</t>
+          <t>-0.870939986021134</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-82.15</t>
+          <t>-0.821540164346142</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-73.19</t>
+          <t>-0.731907430210116</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-73.88</t>
+          <t>-0.738805637337475</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-71.76</t>
+          <t>-0.717586336882129</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-65.35</t>
+          <t>-0.653450960367237</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-76.65</t>
+          <t>-0.76651260929382</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-85.41</t>
+          <t>-0.854095307694504</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-85.52</t>
+          <t>-0.855187268916414</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-83.1</t>
+          <t>-0.831007451951213</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-84.89</t>
+          <t>-0.848946875953433</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-0.840417637130646</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-0.869130002618539</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-0.876387056241874</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-84.99</t>
+          <t>-0.849885970514304</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-84.8</t>
+          <t>-0.848039944337463</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-77.93</t>
+          <t>-0.779306483698974</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-58.13</t>
+          <t>-0.581332762800434</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-70.02</t>
+          <t>-0.700220706668226</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-71.48</t>
+          <t>-0.714833411562888</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-66.76</t>
+          <t>-0.667637653586518</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-70.85</t>
+          <t>-0.708489013826977</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.16</t>
+          <t>-0.741635080176928</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-83.37</t>
+          <t>-0.833717030362701</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-79.67</t>
+          <t>-0.79665339108642</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-81.99</t>
+          <t>-0.819864710798636</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-86.93</t>
+          <t>-0.869263448284494</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-0.888517203924581</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-88.71</t>
+          <t>-0.887133454679317</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-91.8</t>
+          <t>-0.917974073392935</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-89.5</t>
+          <t>-0.895021074120412</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-76.52</t>
+          <t>-0.765244805278221</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-77.83</t>
+          <t>-0.778274585994483</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-85.09</t>
+          <t>-0.850948000229026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-83.04</t>
+          <t>-0.830396865684383</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-0.858119369317948</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-89.78</t>
+          <t>-0.897759332708162</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-93.53</t>
+          <t>-0.935302532950754</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-93.78</t>
+          <t>-0.937787141281457</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-92.92</t>
+          <t>-0.929247760661226</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-93.22</t>
+          <t>-0.932153653005367</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-0.932804632631777</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-94.49</t>
+          <t>-0.944906457650844</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-0.945152117535535</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-0.933439008803355</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>-0.926904285065601</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-0.916582272950665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-0.279664483892432</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-35.78</t>
+          <t>-0.357786519419302</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-0.281517281828087</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-42.13</t>
+          <t>-0.421267639897727</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-51.83</t>
+          <t>-0.518283301911767</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-57.8</t>
+          <t>-0.57795676414311</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-70.53</t>
+          <t>-0.705339819338125</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-66.43</t>
+          <t>-0.664289181782874</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-57.14</t>
+          <t>-0.571386626231736</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.0115221075514189</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>362.64</t>
+          <t>3.62638395802256</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>86.52</t>
+          <t>0.86524530110547</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-82.53</t>
+          <t>-0.825337423699566</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-82.18</t>
+          <t>-0.821755292775371</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-72.88</t>
+          <t>-0.72877140945335</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>121.54</t>
+          <t>1.21536701397886</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>132.49</t>
+          <t>1.32491791090401</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>143.59</t>
+          <t>1.43594354134583</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>0.977028202436268</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>56.55</t>
+          <t>0.565514067658493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>0.127267007229982</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-0.0892117874823584</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-0.0857645494857533</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.000132904054329197</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>0.101736944957507</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.00497566373538127</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.0234419974461528</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>0.127789862812849</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>0.372568584712662</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>0.973027028889546</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-0.177776711731779</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-30.48</t>
+          <t>-0.304849409764347</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>0.519582353724271</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-0.100638243919666</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-39.33</t>
+          <t>-0.393251558518548</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-49.83</t>
+          <t>-0.498273934955808</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-0.718761082076456</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-70.21</t>
+          <t>-0.702085077069407</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-64.82</t>
+          <t>-0.648171855432111</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-64.99</t>
+          <t>-0.649852110084348</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-62.2</t>
+          <t>-0.621953808873413</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-65.46</t>
+          <t>-0.654600281230949</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-53.93</t>
+          <t>-0.539323326557277</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-45.29</t>
+          <t>-0.452890055159163</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-24.27</t>
+          <t>-0.242705129434814</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-93.93</t>
+          <t>-0.939347377450491</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-93.94</t>
+          <t>-0.939365630744573</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-0.907396733976077</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-92.87</t>
+          <t>-0.928749823074894</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-0.940618888352294</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-95.32</t>
+          <t>-0.953164192423928</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-95.34</t>
+          <t>-0.953386918604159</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-95.24</t>
+          <t>-0.95238219577508</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-95.59</t>
+          <t>-0.955941233781905</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-95.83</t>
+          <t>-0.958325492810182</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-96.36</t>
+          <t>-0.963580888829503</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-96.31</t>
+          <t>-0.963099862785045</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-95.59</t>
+          <t>-0.955877898367564</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-95.44</t>
+          <t>-0.954429737843513</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>-0.940817912169609</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-48.84</t>
+          <t>-0.488431693176546</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-54.87</t>
+          <t>-0.548665581517868</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-46.44</t>
+          <t>-0.464410189891025</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-59.3</t>
+          <t>-0.592960222677894</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-63</t>
+          <t>-0.630001550308052</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.07</t>
+          <t>-0.700678076364031</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-62.79</t>
+          <t>-0.627874141337621</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-61.85</t>
+          <t>-0.618500504347875</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-58.73</t>
+          <t>-0.587303088261538</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-62.7</t>
+          <t>-0.626962139327383</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>-0.632732667139753</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-64.19</t>
+          <t>-0.641856426920193</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>-0.642938005872559</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-63.55</t>
+          <t>-0.635507769156658</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-54.13</t>
+          <t>-0.541333995956817</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-73.93</t>
+          <t>-0.739293902184852</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-74.46</t>
+          <t>-0.744637399849869</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-67</t>
+          <t>-0.669983152858752</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-70.95</t>
+          <t>-0.709488198330112</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-78.24</t>
+          <t>-0.782389219796294</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-86.16</t>
+          <t>-0.861550381286485</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-86.7</t>
+          <t>-0.866951695955813</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-86.4</t>
+          <t>-0.863965216967038</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-84.43</t>
+          <t>-0.844282511182706</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-88.29</t>
+          <t>-0.882944140295761</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-90.85</t>
+          <t>-0.908498889466949</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-91.36</t>
+          <t>-0.913614649349266</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-90.43</t>
+          <t>-0.904312015781224</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-90.67</t>
+          <t>-0.906672773906645</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-83.9</t>
+          <t>-0.838978850324936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>0.0741496085712134</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.054511165199655</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>0.332229527532485</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-0.0312539377110164</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>0.181374420038191</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-18.2</t>
+          <t>-0.182042003873757</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.86</t>
+          <t>-0.338629857425876</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-35.14</t>
+          <t>-0.351440081416778</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-25.4</t>
+          <t>-0.253983763031216</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-18.23</t>
+          <t>-0.182343802535541</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-46.56</t>
+          <t>-0.46562366823909</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>-50.9</t>
+          <t>-0.50903215075531</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-77.4</t>
+          <t>-0.773995838170801</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-80.13</t>
+          <t>-0.801268718878758</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>-63.12</t>
+          <t>-0.63124837599478</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>0.0867078682169915</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>-0.106004205838548</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>0.0818134317808721</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.0609014737293276</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>0.105872747411298</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-20.27</t>
+          <t>-0.202665437838112</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-0.236254888743454</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-27.69</t>
+          <t>-0.276943836125332</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-0.353055118530631</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-28.66</t>
+          <t>-0.286568496375619</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-33.05</t>
+          <t>-0.330458416456321</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-0.376098413710345</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>-41.32</t>
+          <t>-0.413152591689196</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-46.39</t>
+          <t>-0.463867046486389</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>-29.78</t>
+          <t>-0.29780728844169</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-28.55</t>
+          <t>-0.285487887615718</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-26.98</t>
+          <t>-0.269798481513165</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-24.33</t>
+          <t>-0.24328276773368</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-43.56</t>
+          <t>-0.435593001501541</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-48.09</t>
+          <t>-0.48085782641862</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-66.02</t>
+          <t>-0.660223098133282</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-69.65</t>
+          <t>-0.696493406053512</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-68.42</t>
+          <t>-0.684210265740404</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-72.44</t>
+          <t>-0.724446322672255</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-83.13</t>
+          <t>-0.831303981289309</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-85.16</t>
+          <t>-0.851639114845608</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-85.45</t>
+          <t>-0.854509379610024</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-86.34</t>
+          <t>-0.863387426354732</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-82.23</t>
+          <t>-0.822287488390847</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-80.17</t>
+          <t>-0.801702629100506</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-91.56</t>
+          <t>-0.915561335819504</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-91.18</t>
+          <t>-0.911812755251211</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-88.44</t>
+          <t>-0.884404506049866</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-88.73</t>
+          <t>-0.887331831553103</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-91.39</t>
+          <t>-0.913912016748228</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-93.52</t>
+          <t>-0.935181345755</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-93.78</t>
+          <t>-0.93778128581435</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-0.939770650214213</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-94.72</t>
+          <t>-0.947152843070531</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-94.94</t>
+          <t>-0.949430339358845</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-95.5</t>
+          <t>-0.955027117334176</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-95.34</t>
+          <t>-0.95343541170357</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-94.51</t>
+          <t>-0.945094631057973</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-95.68</t>
+          <t>-0.956792347796791</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-93.84</t>
+          <t>-0.938371244175448</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-92.19</t>
+          <t>-0.921898660407276</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-0.921286600787402</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-90.08</t>
+          <t>-0.900785163342609</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-90.98</t>
+          <t>-0.909778822833431</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-92.78</t>
+          <t>-0.92784827646527</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-94.6</t>
+          <t>-0.946008228332245</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-94.74</t>
+          <t>-0.947426541927042</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-94.67</t>
+          <t>-0.946702042181105</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-95.36</t>
+          <t>-0.953642548960608</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-95.44</t>
+          <t>-0.954386632183998</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>-0.958753202035848</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>-0.954329413073173</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-94.93</t>
+          <t>-0.949281096292666</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>-0.94076354753201</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-91.99</t>
+          <t>-0.919918348498926</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-26.44</t>
+          <t>-0.264409810165324</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-35.74</t>
+          <t>-0.357354250791834</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-47.21</t>
+          <t>-0.472128293670325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-49.51</t>
+          <t>-0.495139901428357</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-61.96</t>
+          <t>-0.619603210929324</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-67.95</t>
+          <t>-0.679453705109912</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-53.46</t>
+          <t>-0.534613255442786</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-19.93</t>
+          <t>-0.199326385297466</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-19.45</t>
+          <t>-0.194456018730616</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>-0.141896060044645</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-0.218595639383953</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-15.96</t>
+          <t>-0.159649989012484</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-0.0498705485894231</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-0.0536324379201891</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0.672007940905751</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-81.22</t>
+          <t>-0.812245611919432</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-82.13</t>
+          <t>-0.821285777282774</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-78.51</t>
+          <t>-0.785127861259192</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-79.32</t>
+          <t>-0.793210833469458</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-84.95</t>
+          <t>-0.849546499834887</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-0.89190627080252</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-88.8</t>
+          <t>-0.888037590889266</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-89.78</t>
+          <t>-0.897844803048484</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-0.898529949873383</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-88.81</t>
+          <t>-0.888144124631377</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>-0.889455730954608</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-87.83</t>
+          <t>-0.878256078609152</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-83.05</t>
+          <t>-0.830499645541232</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-81.79</t>
+          <t>-0.817910981554389</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-73.4</t>
+          <t>-0.734018184636448</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-83.8</t>
+          <t>-0.837966660006995</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-0.822612997330793</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-81.19</t>
+          <t>-0.811872620679835</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-82.8</t>
+          <t>-0.827962849681467</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-0.84773094865303</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-90.25</t>
+          <t>-0.902486154137278</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-90.24</t>
+          <t>-0.902420086967283</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-89.72</t>
+          <t>-0.897213004859448</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-89.59</t>
+          <t>-0.895862948245965</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-90.93</t>
+          <t>-0.909333786086139</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-92.05</t>
+          <t>-0.920511718037565</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-91.8</t>
+          <t>-0.917976285442526</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-90.48</t>
+          <t>-0.904755397342519</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-90.17</t>
+          <t>-0.901707614743058</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-85.12</t>
+          <t>-0.85122231226204</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>485.11</t>
+          <t>4.85111188737578</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>458.55</t>
+          <t>4.58547004813691</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>418.28</t>
+          <t>4.18284328948331</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>446.33</t>
+          <t>4.46333374991935</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>463.85</t>
+          <t>4.63850965139108</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>4.24002717024417</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>422.79</t>
+          <t>4.22787865794251</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>429.44</t>
+          <t>4.29440852162096</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>464.83</t>
+          <t>4.64829720486903</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>425.83</t>
+          <t>4.2583009602833</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>430.94</t>
+          <t>4.30940639917582</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>422.54</t>
+          <t>4.22539170413759</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>443.93</t>
+          <t>4.4392721427172</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>395.8</t>
+          <t>3.95802444390789</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>387.95</t>
+          <t>3.8794693225926</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>290.67</t>
+          <t>2.90670752951812</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>272.81</t>
+          <t>2.72808892505138</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>270.16</t>
+          <t>2.70155840208691</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>284.1</t>
+          <t>2.84097424425232</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>274.88</t>
+          <t>2.74882541570613</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>224.3</t>
+          <t>2.24299249928866</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>220.42</t>
+          <t>2.20424468271401</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>219.81</t>
+          <t>2.1980681115981</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>232.63</t>
+          <t>2.32630651076588</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>203.86</t>
+          <t>2.03864169195069</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>188.85</t>
+          <t>1.88845720527643</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>175.96</t>
+          <t>1.75964776647118</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>184.45</t>
+          <t>1.84447591557054</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>157.9</t>
+          <t>1.57900650832425</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>192.85</t>
+          <t>1.92850233679289</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
